--- a/data/trans_orig/IP16A06-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP16A06-Edad-trans_orig.xlsx
@@ -1115,7 +1115,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>3568</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3523</t>
+          <t>3881</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>4,12%</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>47510</t>
+          <t>47392</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>90658</t>
+          <t>90300</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3171</t>
+          <t>3030</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4262</t>
+          <t>4201</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>556</t>
+          <t>544</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5157</t>
+          <t>5211</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,24%</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>19336</t>
+          <t>19477</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,91%</t>
+          <t>86,54%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>19604</t>
+          <t>19665</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>82,14%</t>
+          <t>82,4%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>41216</t>
+          <t>41162</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>45817</t>
+          <t>45829</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,88%</t>
+          <t>88,76%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,83%</t>
         </is>
       </c>
     </row>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4514</t>
+          <t>4364</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1801,7 +1801,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4358</t>
+          <t>4389</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1065</t>
+          <t>666</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6170</t>
+          <t>6098</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,71%</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>26029</t>
+          <t>26179</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,22%</t>
+          <t>85,71%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>35080</t>
+          <t>35049</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>88,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>63811</t>
+          <t>63883</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>68916</t>
+          <t>69315</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,18%</t>
+          <t>91,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>99,05%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>597</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5792</t>
+          <t>5896</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1203</t>
+          <t>1217</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7641</t>
+          <t>7719</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>2461</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9969</t>
+          <t>9327</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,46%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>119513</t>
+          <t>119409</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>124705</t>
+          <t>124708</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>136278</t>
+          <t>136200</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>142716</t>
+          <t>142702</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>259255</t>
+          <t>259897</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>266769</t>
+          <t>266763</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -3027,7 +3027,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3368</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3342</t>
+          <t>3541</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,53%</t>
         </is>
       </c>
     </row>
@@ -3135,7 +3135,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>61879</t>
+          <t>61594</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -3150,7 +3150,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3205,7 +3205,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>136576</t>
+          <t>136377</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -3220,7 +3220,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3708,12 +3708,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>676</t>
+          <t>672</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5471</t>
+          <t>5975</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3743,12 +3743,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>726</t>
+          <t>694</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6622</t>
+          <t>5962</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1962</t>
+          <t>2119</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8957</t>
+          <t>9825</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>14,51%</t>
         </is>
       </c>
     </row>
@@ -3821,12 +3821,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>29690</t>
+          <t>29186</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>34485</t>
+          <t>34489</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>84,44%</t>
+          <t>83,01%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3856,12 +3856,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>25941</t>
+          <t>26601</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>31837</t>
+          <t>31869</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,66%</t>
+          <t>81,69%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3891,12 +3891,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>58767</t>
+          <t>57899</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>65762</t>
+          <t>65605</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,77%</t>
+          <t>85,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>96,87%</t>
         </is>
       </c>
     </row>
@@ -4051,12 +4051,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>801</t>
+          <t>816</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7718</t>
+          <t>7603</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>717</t>
+          <t>691</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7266</t>
+          <t>6602</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2647</t>
+          <t>2626</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10913</t>
+          <t>11063</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,92%</t>
         </is>
       </c>
     </row>
@@ -4164,12 +4164,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>179274</t>
+          <t>179389</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>186191</t>
+          <t>186176</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,56%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>184212</t>
+          <t>184876</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>190761</t>
+          <t>190787</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>367557</t>
+          <t>367407</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>375823</t>
+          <t>375844</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,12 +4249,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,31%</t>
         </is>
       </c>
     </row>
@@ -4666,7 +4666,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3353</t>
+          <t>3281</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4681,7 +4681,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4701,7 +4701,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3334</t>
+          <t>3272</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4716,7 +4716,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,26%</t>
         </is>
       </c>
     </row>
@@ -4774,7 +4774,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>27565</t>
+          <t>27637</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -4789,7 +4789,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,15%</t>
+          <t>89,39%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4809,7 +4809,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>58877</t>
+          <t>58939</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -4824,7 +4824,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -5660,7 +5660,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4099</t>
+          <t>3803</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5675,7 +5675,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5695,7 +5695,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4325</t>
+          <t>4043</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5710,7 +5710,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>580</t>
+          <t>589</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>5578</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,81%</t>
         </is>
       </c>
     </row>
@@ -5768,7 +5768,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>32140</t>
+          <t>32436</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -5783,7 +5783,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,69%</t>
+          <t>89,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5803,7 +5803,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>22716</t>
+          <t>22998</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -5818,7 +5818,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,01%</t>
+          <t>85,05%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>57980</t>
+          <t>57703</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>62701</t>
+          <t>62692</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5853,12 +5853,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,62%</t>
+          <t>91,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,07%</t>
         </is>
       </c>
     </row>
@@ -6003,7 +6003,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3906</t>
+          <t>4043</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6018,7 +6018,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>584</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5602</t>
+          <t>5067</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1113</t>
+          <t>1107</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6298</t>
+          <t>6564</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,11%</t>
         </is>
       </c>
     </row>
@@ -6111,7 +6111,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>158630</t>
+          <t>158493</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -6126,7 +6126,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>142523</t>
+          <t>143058</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>147533</t>
+          <t>147541</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>304363</t>
+          <t>304097</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>309548</t>
+          <t>309554</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6196,7 +6196,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">

--- a/data/trans_orig/IP16A06-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP16A06-Edad-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -835,47 +835,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>29655</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>29035</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>29655</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -948,57 +948,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>29655</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>29655</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>29655</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>29035</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>29035</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>29035</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>29655</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>29655</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>29655</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1065,107 +1065,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3472</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,37%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>6,81%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>700</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>3568</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,37%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>3495</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,74%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>7,0%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>700</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>3881</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,74%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>3,71%</t>
         </is>
       </c>
     </row>
@@ -1178,72 +1178,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>50260</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>47488</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>50960</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>98,63%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>93,19%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>43221</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>50260</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>47392</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>50960</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>98,63%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>90300</t>
+          <t>90686</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1291,57 +1291,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>50960</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>50960</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>50960</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>43221</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>43221</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>43221</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>50960</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>50960</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>50960</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1408,72 +1408,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1278</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>4391</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>5,35%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>18,4%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>654</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3030</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>3162</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>2,9%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>13,46%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>1278</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>4201</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>5,35%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>544</t>
+          <t>548</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5211</t>
+          <t>5422</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,69%</t>
         </is>
       </c>
     </row>
@@ -1521,74 +1521,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>22588</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>19475</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>23866</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>94,65%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>81,6%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>21853</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>19477</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>19345</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>22507</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>97,1%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>86,54%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>85,95%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>22588</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>19665</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>23866</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>94,65%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>82,4%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>66</t>
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>41162</t>
+          <t>40951</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>45829</t>
+          <t>45825</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,76%</t>
+          <t>88,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,82%</t>
         </is>
       </c>
     </row>
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>23866</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>23866</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>23866</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>22507</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>22507</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>22507</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>23866</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>23866</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>23866</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1756,67 +1756,67 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>1235</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3835</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>3,13%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>9,72%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
           <t>1389</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>4364</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>4861</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>4,55%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>14,29%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>1235</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>4389</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>3,13%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>666</t>
+          <t>603</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6098</t>
+          <t>6254</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,94%</t>
         </is>
       </c>
     </row>
@@ -1864,74 +1864,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>38203</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>35603</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>39438</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>96,87%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>90,28%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>29154</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>26179</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>25682</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>30543</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>95,45%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>85,71%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>84,08%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>38203</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>35049</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>39438</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>96,87%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>88,87%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>100</t>
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>63883</t>
+          <t>63727</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>69315</t>
+          <t>69378</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,29%</t>
+          <t>91,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,14%</t>
         </is>
       </c>
     </row>
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>39438</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>39438</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>39438</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>45</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>30543</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>30543</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>30543</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>39438</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>39438</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>39438</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2094,72 +2094,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>3213</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1184</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>7061</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>2,23%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,82%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>4,91%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>2043</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>597</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>5896</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>596</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>5677</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>1,63%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,48%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>4,7%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>3213</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>1217</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>7719</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>2,23%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,85%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2461</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9327</t>
+          <t>9806</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,64%</t>
         </is>
       </c>
     </row>
@@ -2207,74 +2207,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>140706</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>136858</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>142735</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>97,77%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>95,09%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,18%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>187</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>123262</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>119409</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>124708</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>119628</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>124709</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>98,37%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>95,3%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>95,47%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>99,52%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>210</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>140706</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>136200</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>142702</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>97,77%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>94,64%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>99,15%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>397</t>
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>259897</t>
+          <t>259418</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>266763</t>
+          <t>266614</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,03%</t>
         </is>
       </c>
     </row>
@@ -2320,57 +2320,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>143919</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>143919</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>143919</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>190</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>125305</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>125305</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>125305</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>143919</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>143919</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>143919</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2490,7 +2490,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2501,7 +2501,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2782,47 +2782,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>51749</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>72</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>48856</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>51749</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -2895,57 +2895,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>51749</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>51749</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>51749</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>72</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>48856</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>48856</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>48856</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>51749</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>51749</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>51749</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3012,107 +3012,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>656</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>3653</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3774</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>1,01%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>5,6%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>5,78%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>656</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>3044</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,47%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>656</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>3541</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,18%</t>
         </is>
       </c>
     </row>
@@ -3125,74 +3125,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>74671</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>92</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>64591</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>61594</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>61473</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>65247</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>98,99%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>94,4%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>94,22%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>74671</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>196</t>
@@ -3205,7 +3205,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>136377</t>
+          <t>136874</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -3220,7 +3220,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3238,57 +3238,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>74671</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>74671</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>74671</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>65247</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>65247</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>65247</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>74671</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>74671</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>74671</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3468,47 +3468,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>32494</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>37728</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>32494</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -3581,57 +3581,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>32494</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>32494</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>32494</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>37728</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>37728</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>37728</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>32494</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>32494</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>32494</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3698,72 +3698,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2667</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>686</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>6084</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>8,19%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2,11%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>18,69%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>2292</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>672</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>5975</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>678</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>6506</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>6,52%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>1,91%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>16,99%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>2667</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>694</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>5962</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>8,19%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2119</t>
+          <t>2102</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9825</t>
+          <t>9569</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,13%</t>
         </is>
       </c>
     </row>
@@ -3811,72 +3811,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>29896</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>26479</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>31877</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>91,81%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>81,31%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>97,89%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>48</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>32869</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>29186</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>34489</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>28655</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>34483</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>93,48%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>83,01%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>98,09%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>29896</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>26601</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>31869</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>91,81%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,69%</t>
+          <t>81,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3891,12 +3891,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>57899</t>
+          <t>58155</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>65605</t>
+          <t>65622</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,49%</t>
+          <t>85,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,9%</t>
         </is>
       </c>
     </row>
@@ -3924,57 +3924,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>32563</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>32563</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>32563</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>51</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>35161</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>35161</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>35161</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>32563</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>32563</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>32563</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4046,67 +4046,67 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>2667</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>689</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>6824</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1,39%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,36%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>3,56%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
           <t>2947</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>816</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>7603</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>798</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>7263</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>1,58%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>4,07%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>2667</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>691</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>6602</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>1,39%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2626</t>
+          <t>2631</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>11063</t>
+          <t>11380</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,01%</t>
         </is>
       </c>
     </row>
@@ -4154,72 +4154,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>267</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>188811</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>184654</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>190789</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>98,61%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>96,44%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,64%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>265</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>184045</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>179389</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>186176</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>179729</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>186194</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>98,42%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>95,93%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>99,56%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>267</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>188811</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>184876</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>190787</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>98,61%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,57%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>367407</t>
+          <t>367090</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>375844</t>
+          <t>375839</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,12 +4249,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,3%</t>
         </is>
       </c>
     </row>
@@ -4267,57 +4267,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>271</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>191478</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>191478</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>191478</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>269</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>186992</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>186992</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>186992</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>271</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>191478</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>191478</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>191478</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4437,7 +4437,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4448,7 +4448,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4616,107 +4616,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>646</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3195</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2,09%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>10,33%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>646</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3281</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>2,09%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>3649</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>1,04%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>10,61%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>646</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>3272</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>1,04%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,87%</t>
         </is>
       </c>
     </row>
@@ -4729,72 +4729,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>30272</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>27723</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>30918</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>97,91%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>89,67%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>51</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>31293</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>30272</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>27637</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>30918</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>97,91%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,39%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4809,7 +4809,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>58939</t>
+          <t>58562</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -4824,7 +4824,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4842,57 +4842,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>30918</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>30918</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>30918</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>51</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>31293</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>31293</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>31293</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>30918</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>30918</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>30918</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5072,47 +5072,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>47366</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>51100</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>47366</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -5185,57 +5185,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>47366</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>47366</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>47366</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>51100</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>51100</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>51100</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>47366</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>47366</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>47366</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5415,47 +5415,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>42800</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>43903</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>42800</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -5528,57 +5528,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>42800</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>42800</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>42800</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>43903</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>43903</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>43903</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>42800</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>42800</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>42800</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5650,67 +5650,67 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>1214</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3884</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>4,49%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>14,36%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
           <t>1141</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>3803</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>4048</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>3,15%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>10,49%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>1214</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>4043</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>4,49%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>589</t>
+          <t>598</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5578</t>
+          <t>5590</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,83%</t>
         </is>
       </c>
     </row>
@@ -5758,74 +5758,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>25827</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>23157</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>27041</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>95,51%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>85,64%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>35098</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>32436</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>32191</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>36239</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>96,85%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>89,51%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>88,83%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>25827</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>22998</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>27041</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>95,51%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>85,05%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>85</t>
@@ -5838,12 +5838,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>57703</t>
+          <t>57691</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>62692</t>
+          <t>62683</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5853,12 +5853,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,19%</t>
+          <t>91,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,05%</t>
         </is>
       </c>
     </row>
@@ -5871,57 +5871,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>27041</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>27041</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>27041</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>52</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>36239</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>36239</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>36239</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>27041</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>27041</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>27041</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5988,72 +5988,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1859</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>589</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>5531</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1,26%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>3,73%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>1141</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>4043</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>3951</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,7%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>2,49%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>1859</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>584</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>5067</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>1,26%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1107</t>
+          <t>1048</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6564</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -6101,74 +6101,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>146266</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>142594</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>147536</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>98,74%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>96,27%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,6%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>243</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>161395</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>158493</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>158585</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>162536</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>99,3%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>97,51%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>97,57%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>146266</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>143058</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>147541</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>98,74%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>96,58%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>99,61%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>455</t>
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>304097</t>
+          <t>304219</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>309554</t>
+          <t>309613</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6196,12 +6196,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,66%</t>
         </is>
       </c>
     </row>
@@ -6214,57 +6214,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>148125</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>148125</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>148125</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>245</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>162536</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>162536</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>162536</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>148125</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>148125</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>148125</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
